--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Denetim" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ozet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Yeniden Üretilecekler" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ozet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Denetim'!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Yeniden Üretilecekler'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +174,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8399,6 +8404,1035 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gorsel / Item Adi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Metni (Ingilizce - Gemini'ye yapistirilacak)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cikti Dosya Adi</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Referans Gorsel Dosyasi</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>En-Boy Orani</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Neden yeniden isteniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>B-00</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>body (skin layer)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: The bare body itself, as a SKIN LAYER. Paint every cell except "weapon": head (bald head, simple ear, neck, a plain profile face with only a small nose and brow line, no hair), torso, upper arm, forearm, hand (closed loosely, thumb forward), thigh, shin, foot (bare foot, sole on the red-dot line). Paint it in NEUTRAL LIGHT GREY tones only (#D8D8D8 base, #A8A8A8 shade, dark ink contour) — the game tints it with each character's skin colour.
+Cells: head, torso, upper_arm, forearm, hand, thigh, shin, foot.</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>body.png</t>
+        </is>
+      </c>
+      <c r="F2" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="n">
+        <v>52101</v>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>hat_felt (Felt Cap)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A soft felt cap in faded brown (#6B5238), the kind worn by nomads and drovers: rounded crown, a short upturned brim at the front, a stitched seam along the side. It sits on top of the head down to the ears; the face stays empty.
+Cells: head only.</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>hat_felt.png</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n">
+        <v>52102</v>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>hat_hood (Travelling Hood)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A grey-brown wool travelling hood (#4D4D57) pulled over the head, drawn slightly forward over the brow, falling to the neck and the top of the shoulders. The face opening stays empty. The hood's lower edge may spill a little into the top of the torso cell as a short shoulder cape.
+Cells: head (main), torso (only the short shoulder cape, top edge).</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>hat_hood.png</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>52103</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>shirt_linen (Linen Shirt)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A plain undyed linen shirt (#D1C7A8), loose and slightly creased, collarless with a short slit at the neck, long sleeves ending just above the wrist, hem tucked at the waist. Thin, soft fabric.
+Cells: torso, upper_arm, forearm.</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>shirt_linen.png</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>52104</v>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>shirt_dyed (Dyed Shirt)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A woad-dyed blue linen shirt (#5C7594), faded unevenly from sun and washing, a narrow woven band along the collar and cuffs in pale gold (#DCB357). Long sleeves to the wrist, belted at the waist with a thin cord.
+Cells: torso, upper_arm, forearm.</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>shirt_dyed.png</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>52105</v>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>jacket_wool (Wool Coat)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A heavy brown wool kaftan-style coat (#614733), wrapped across the chest and tied at the side, reaching mid-thigh, long sleeves slightly wider at the cuff, a darker felt trim along the front edge and hem. Worn patches at the elbows.
+Cells: torso (with the coat's skirt hanging below the hip), upper_arm, forearm, thigh (only the coat's skirt over the upper thigh).</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>jacket_wool.png</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>52106</v>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>jacket_leather (Leather Jerkin)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A dark oiled leather jerkin (#4D3324), sleeveless body with short cap sleeves over the shoulder, laced up the front with leather thongs, scuffed and creased, a broad belt with a simple iron buckle.
+Cells: torso, upper_arm (cap sleeve only, top third).</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>jacket_leather.png</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>52107</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>gloves_leather (Leather Gloves)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Brown work gloves of thick leather (#57402E) with a short flared cuff that covers the lower forearm, stitched seams on the back of the hand.
+Cells: hand, forearm (only the cuff, near the blue-dot end).</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>gloves_leather.png</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n">
+        <v>52108</v>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>pants_wool (Wool Trousers)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Dark grey-brown wool trousers (#47423D), loose at the thigh, wrapped tight below the knee with cloth puttee bands up the shin.
+Cells: thigh, shin.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>pants_wool.png</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>B-09</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n">
+        <v>52109</v>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>pants_canvas (Canvas Trousers)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Light sand-coloured canvas trousers (#948A70), baggy in the Anatolian şalvar cut — full at the thigh, gathered at the ankle — dusty at the hem, a patched knee.
+Cells: thigh, shin.</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>pants_canvas.png</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>52110</v>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>shoes_boots (Riding Boots)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Tall soft leather riding boots (#382920), reaching just below the knee, a slightly upturned toe, worn creases at the ankle, a thin sole. The sole must sit exactly on the red dot's horizontal line in the foot cell (that line is the ground).
+Cells: shin (boot shaft), foot.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>shoes_boots.png</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>52111</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>shoes_sandals (Sandals)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Simple leather sandals (#80664D): a flat sole with straps across the foot and two thin straps wrapping the lower ankle. The foot itself is NOT painted — only the sole and straps (the body layer shows through between the straps; leave those gaps empty).
+Cells: foot, shin (only the ankle straps at the lower end).</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>shoes_sandals.png</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>52112</v>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_1 (Leather Armor)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Hardened boiled-leather armour: a thick quilted-and-leather cuirass covering chest and back to the hip, overlapping leather strips hanging over the upper thigh, small leather shoulder guards. Brown and dark tan (#5A3F2A / #7A5A3C), stitched, scuffed, matte.
+Cells: torso, upper_arm (shoulder guard, top third), thigh (hanging strips, top third).</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_1.png</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>B-13</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>52113</v>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_2 (Chain Shirt)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A riveted iron mail shirt (cold steel #6F7A82, darker in the folds) reaching mid-thigh, with elbow-length mail sleeves, worn over a quilted under-coat whose padded edge shows at the neck and hem. The mail is shown as a fine ring texture, not individual shiny rings; dull, slightly rusty.
+Cells: torso, upper_arm, thigh (mail skirt, top half).</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_2.png</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>B-14</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>52114</v>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_3 (Plate Armor)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: Lamellar and plate armour of a veteran caravan guard: a chest of laced iron lamellae over mail, a rounded pauldron on the shoulder, a plate vambrace on the forearm, lamellar tassets over the thigh, a riveted iron gorget at the neck. Dull iron (#6F7A82) with dark leather lacing and a thin pale-gold (#DCB357) edge on the pauldron — worn, dented, never polished.
+Cells: torso, upper_arm, forearm, thigh.</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>armor_tier_3.png</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>B-15</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>52115</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_1 (Caravan Sword)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A plain iron arming sword for caravan guards: straight single-edged blade, simple cross guard, leather-wrapped grip, round iron pommel. Grey steel, a few nicks on the edge. Grip on the red dot, pommel just above it, blade pointing straight DOWN toward the blue dot and beyond.
+Cells: weapon only.</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_1.png</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>B-16</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>52116</v>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_2 (Master's Sword)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A well-made curved sabre (kılıç): a slightly curved single-edged blade widening a little toward the tip, a short straight guard with downturned ends, a grip wrapped in dark leather, a brass (#DCB357, dulled) cap on the pommel. Grip on the red dot, blade pointing DOWN, the curve bending toward the right.
+Cells: weapon only.</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_2.png</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>B-17</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>52117</v>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_3 (Falcon Sword)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A fine old sabre of a master smith: a deeply curved blade with a subtle wavy forging pattern in the steel, a pale-gold (#DCB357) guard whose two ends are shaped like folded falcon wings, a grip bound in dark red cord (#A83029), a falcon-head pommel. Still worn and matte, not glowing. Grip on the red dot, blade pointing DOWN, curve bending toward the right.
+Cells: weapon only.</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>weapon_tier_3.png</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n">
+        <v>52118</v>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>amulet_ward (Ward Charm)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A small folded triangular cloth charm (muska) in faded red wool, stitched shut, hanging from a dark cord around the neck; the cord runs up toward the neck, the charm rests on the upper chest.
+Cells: torso only (upper chest, near the red dot).</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>amulet_ward.png</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>B-19</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>52119</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>amulet_wolf_fang (Wolf Fang Pendant)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A single large yellowed wolf fang bound with a leather thong, hung on a braided cord around the neck, resting on the upper chest.
+Cells: torso only (upper chest).</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>amulet_wolf_fang.png</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>B-20</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>52120</v>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>amulet_courage (Courage Charm)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 2:3. Use the attached template.
+ITEM: A flat bronze disc pendant (dull #B08A4A), its face hammered with a simple radiating pattern (no letters, no religious sign), on a thin chain around the neck, resting on the upper chest.
+Cells: torso only (upper chest).</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>amulet_courage.png</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>part_sheet_template.png</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>C-p3-agility</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>53102</v>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>a leaping hare mid-stride</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 1:1. ICON: a leaping hare mid-stride.</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>p3_agility.png</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>İlk teslimatta gelen dosya kendi dosya adıyla uyuşmuyordu (yumruk+halka, tavşan değil) - aynen aynı prompt'la tekrar iste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>C-p5-scout</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>53202</v>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>a hawk perched on a gloved fist</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Aspect ratio 1:1. ICON: a hawk perched on a gloved fist.</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>p5_scout.png</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>İlk teslimatta gelen dosya kendi dosya adıyla uyuşmuyordu (bir insan portresi, şahin değil) - aynen aynı prompt'la tekrar iste.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Denetim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Yeniden Üretilecekler" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ozet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Olay Kartlari 2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Denetim'!$A$1:$M$124</definedName>
@@ -128,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -177,6 +178,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,25 +639,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>A-a</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="26" t="n">
         <v>41201</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>wildlife_ambush</t>
         </is>
@@ -658,27 +668,27 @@
 AVOID: text, frame, clearly identifiable animal, gore.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>e6a_wildlife.jpg</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -691,25 +701,25 @@
       <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>A-b</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="26" t="n">
         <v>41202</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>wolf_pack</t>
         </is>
@@ -720,27 +730,27 @@
 AVOID: text, frame, cartoon wolves, gore.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>e6b_wolves.jpg</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -753,25 +763,25 @@
       <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>A-c</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="26" t="n">
         <v>41203</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>bandit_ambush</t>
         </is>
@@ -782,27 +792,27 @@
 AVOID: text, frame, heroic poses, shiny armour, gore.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>e6c_bandits.jpg</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -815,25 +825,25 @@
       <c r="M4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>A-d</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="26" t="n">
         <v>41204</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>guard_checkpoint</t>
         </is>
@@ -844,27 +854,27 @@
 AVOID: text, frame, heraldry, symbols on the banner, crosses, crescents.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>e6d_guard.jpg</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -877,25 +887,25 @@
       <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>A-e</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="26" t="n">
         <v>41205</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>traveler_wanderer</t>
         </is>
@@ -906,27 +916,27 @@
 AVOID: text, frame, detailed face.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>e6e_traveler.jpg</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -939,25 +949,25 @@
       <c r="M6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>A-f</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="26" t="n">
         <v>41206</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>merchant_caravan</t>
         </is>
@@ -968,27 +978,27 @@
 AVOID: text, frame, horses pulling carts, camels.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>e6f_merchant.jpg</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1001,25 +1011,25 @@
       <c r="M7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>A-g</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="26" t="n">
         <v>41207</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>pilgrim</t>
         </is>
@@ -1030,27 +1040,27 @@
 AVOID: text, frame, crosses, prayer beads of a real religion, halos.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>e6g_pilgrim.jpg</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1063,25 +1073,25 @@
       <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>A-h</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="26" t="n">
         <v>41208</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>roadside_shrine</t>
         </is>
@@ -1092,27 +1102,27 @@
 AVOID: text, frame, carved symbols, crosses, crescents, statues of gods.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>e6h_shrine.jpg</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1125,25 +1135,25 @@
       <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>A-i</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="26" t="n">
         <v>41209</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>mountain_pass</t>
         </is>
@@ -1154,27 +1164,27 @@
 AVOID: text, frame, people, buildings.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>e6i_pass.jpg</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1187,25 +1197,25 @@
       <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>A-j</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="26" t="n">
         <v>41210</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>hamlet_wounded</t>
         </is>
@@ -1216,27 +1226,27 @@
 AVOID: text, frame, gore, graphic wounds.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>e6j_hamlet.jpg</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1249,25 +1259,25 @@
       <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>A-k</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="26" t="n">
         <v>41211</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>frontier_outpost</t>
         </is>
@@ -1278,27 +1288,27 @@
 AVOID: text, frame, heraldry or symbols on the flag.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t>e6k_outpost.jpg</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1311,25 +1321,25 @@
       <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>A-l</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="26" t="n">
         <v>41212</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>mine_collapse</t>
         </is>
@@ -1340,27 +1350,27 @@
 AVOID: text, frame, gore, bodies.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>e6l_mine.jpg</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1373,25 +1383,25 @@
       <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>A-m</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="26" t="n">
         <v>41213</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>failing_bridge</t>
         </is>
@@ -1402,27 +1412,27 @@
 AVOID: text, frame, people.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>e6m_bridge.jpg</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1435,25 +1445,25 @@
       <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>A-n</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="26" t="n">
         <v>41214</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>storm_weather</t>
         </is>
@@ -1464,27 +1474,27 @@
 AVOID: text, frame, people.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>e6n_storm.jpg</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1497,25 +1507,25 @@
       <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>A-o</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="26" t="n">
         <v>41215</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>landslide</t>
         </is>
@@ -1526,27 +1536,27 @@
 AVOID: text, frame, people.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>e6o_landslide.jpg</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1559,25 +1569,25 @@
       <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>A-p</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="26" t="n">
         <v>41216</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>broken_wagon</t>
         </is>
@@ -1588,27 +1598,27 @@
 AVOID: text, frame, bodies.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>e6p_wagon.jpg</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1621,25 +1631,25 @@
       <c r="M17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>A-q</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="26" t="n">
         <v>41217</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>camp_night</t>
         </is>
@@ -1650,27 +1660,27 @@
 AVOID: text, frame, cheerful mood, detailed faces.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>e6q_camp.jpg</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1683,25 +1693,25 @@
       <c r="M18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>A-r</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="26" t="n">
         <v>41218</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>wayside_grave</t>
         </is>
@@ -1712,27 +1722,27 @@
 AVOID: text, frame, crosses, carved letters or symbols.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>e6r_grave.jpg</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1745,25 +1755,25 @@
       <c r="M19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>A-s</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="26" t="n">
         <v>41219</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>creditor_rider</t>
         </is>
@@ -1774,27 +1784,27 @@
 AVOID: text, frame, readable writing on the document.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="26" t="inlineStr">
         <is>
           <t>e6s_creditor.jpg</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1807,25 +1817,25 @@
       <c r="M20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>A-t</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="26" t="n">
         <v>41220</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>world_news</t>
         </is>
@@ -1836,27 +1846,27 @@
 AVOID: readable text, letters, numbers, frame.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="26" t="inlineStr">
         <is>
           <t>e6t_news.jpg</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1869,25 +1879,25 @@
       <c r="M21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Etkinlik karti illustrasyonlari (Event card illustrations)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>A-u</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="26" t="n">
         <v>41221</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>forgotten_cache</t>
         </is>
@@ -1898,27 +1908,27 @@
 AVOID: text, frame, piles of treasure.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>e6u_cache.jpg</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1931,25 +1941,25 @@
       <c r="M22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>B-00</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="26" t="n">
         <v>52000</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>body (skin layer)</t>
         </is>
@@ -1961,27 +1971,27 @@
 Cells: head, torso, upper_arm, forearm, hand, thigh, shin, foot.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="26" t="inlineStr">
         <is>
           <t>body.png</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1998,25 +2008,25 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="26" t="n">
         <v>52101</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>hat_felt (Felt Cap)</t>
         </is>
@@ -2028,27 +2038,27 @@
 Cells: head only.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="26" t="inlineStr">
         <is>
           <t>hat_felt.png</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2065,25 +2075,25 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>B-02</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="26" t="n">
         <v>52102</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>hat_hood (Travelling Hood)</t>
         </is>
@@ -2095,27 +2105,27 @@
 Cells: head (main), torso (only the short shoulder cape, top edge).</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="26" t="inlineStr">
         <is>
           <t>hat_hood.png</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2132,25 +2142,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="26" t="n">
         <v>52103</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>shirt_linen (Linen Shirt)</t>
         </is>
@@ -2162,27 +2172,27 @@
 Cells: torso, upper_arm, forearm.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="26" t="inlineStr">
         <is>
           <t>shirt_linen.png</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2199,25 +2209,25 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="26" t="n">
         <v>52104</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>shirt_dyed (Dyed Shirt)</t>
         </is>
@@ -2229,27 +2239,27 @@
 Cells: torso, upper_arm, forearm.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="26" t="inlineStr">
         <is>
           <t>shirt_dyed.png</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2266,25 +2276,25 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>B-05</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="26" t="n">
         <v>52105</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>jacket_wool (Wool Coat)</t>
         </is>
@@ -2296,27 +2306,27 @@
 Cells: torso (with the coat's skirt hanging below the hip), upper_arm, forearm, thigh (only the coat's skirt over the upper thigh).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>jacket_wool.png</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2333,25 +2343,25 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>B-06</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="26" t="n">
         <v>52106</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>jacket_leather (Leather Jerkin)</t>
         </is>
@@ -2363,27 +2373,27 @@
 Cells: torso, upper_arm (cap sleeve only, top third).</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="26" t="inlineStr">
         <is>
           <t>jacket_leather.png</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2400,25 +2410,25 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>B-07</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="26" t="n">
         <v>52107</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>gloves_leather (Leather Gloves)</t>
         </is>
@@ -2430,27 +2440,27 @@
 Cells: hand, forearm (only the cuff, near the blue-dot end).</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="26" t="inlineStr">
         <is>
           <t>gloves_leather.png</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2467,25 +2477,25 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="26" t="n">
         <v>52108</v>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>pants_wool (Wool Trousers)</t>
         </is>
@@ -2497,27 +2507,27 @@
 Cells: thigh, shin.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>pants_wool.png</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2534,25 +2544,25 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>B-09</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="26" t="n">
         <v>52109</v>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>pants_canvas (Canvas Trousers)</t>
         </is>
@@ -2564,27 +2574,27 @@
 Cells: thigh, shin.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="26" t="inlineStr">
         <is>
           <t>pants_canvas.png</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2601,25 +2611,25 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>B-10</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="26" t="n">
         <v>52110</v>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>shoes_boots (Riding Boots)</t>
         </is>
@@ -2631,27 +2641,27 @@
 Cells: shin (boot shaft), foot.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="26" t="inlineStr">
         <is>
           <t>shoes_boots.png</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2668,25 +2678,25 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>B-11</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="26" t="n">
         <v>52111</v>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>shoes_sandals (Sandals)</t>
         </is>
@@ -2698,27 +2708,27 @@
 Cells: foot, shin (only the ankle straps at the lower end).</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="26" t="inlineStr">
         <is>
           <t>shoes_sandals.png</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2735,25 +2745,25 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>B-12</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="26" t="n">
         <v>52112</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>armor_tier_1 (Leather Armor)</t>
         </is>
@@ -2765,27 +2775,27 @@
 Cells: torso, upper_arm (shoulder guard, top third), thigh (hanging strips, top third).</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="26" t="inlineStr">
         <is>
           <t>armor_tier_1.png</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2802,25 +2812,25 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>B-13</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="26" t="n">
         <v>52113</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>armor_tier_2 (Chain Shirt)</t>
         </is>
@@ -2832,27 +2842,27 @@
 Cells: torso, upper_arm, thigh (mail skirt, top half).</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="26" t="inlineStr">
         <is>
           <t>armor_tier_2.png</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2869,25 +2879,25 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>B-14</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="26" t="n">
         <v>52114</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>armor_tier_3 (Plate Armor)</t>
         </is>
@@ -2899,27 +2909,27 @@
 Cells: torso, upper_arm, forearm, thigh.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>armor_tier_3.png</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2936,25 +2946,25 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>B-15</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="26" t="n">
         <v>52115</v>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_1 (Caravan Sword)</t>
         </is>
@@ -2966,27 +2976,27 @@
 Cells: weapon only.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_1.png</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3003,25 +3013,25 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>B-16</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="26" t="n">
         <v>52116</v>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_2 (Master's Sword)</t>
         </is>
@@ -3033,27 +3043,27 @@
 Cells: weapon only.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_2.png</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3070,25 +3080,25 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>B-17</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="26" t="n">
         <v>52117</v>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_3 (Falcon Sword)</t>
         </is>
@@ -3100,27 +3110,27 @@
 Cells: weapon only.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>weapon_tier_3.png</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3137,25 +3147,25 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>B-18</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="26" t="n">
         <v>52118</v>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>amulet_ward (Ward Charm)</t>
         </is>
@@ -3167,27 +3177,27 @@
 Cells: torso only (upper chest, near the red dot).</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>amulet_ward.png</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3204,25 +3214,25 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>B-19</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="26" t="n">
         <v>52119</v>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>amulet_wolf_fang (Wolf Fang Pendant)</t>
         </is>
@@ -3234,27 +3244,27 @@
 Cells: torso only (upper chest).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>amulet_wolf_fang.png</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3271,25 +3281,25 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Kiyafet parca sayfalari (Wardrobe part sheets)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>B-20</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="26" t="n">
         <v>52120</v>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>amulet_courage (Courage Charm)</t>
         </is>
@@ -3301,27 +3311,27 @@
 Cells: torso only (upper chest).</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>amulet_courage.png</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>part_sheet_template.png</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I43" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="26" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3338,25 +3348,25 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>C-p3-strength</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="26" t="n">
         <v>53101</v>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>a clenched fist gripping a short iron bar</t>
         </is>
@@ -3366,27 +3376,27 @@
           <t>Aspect ratio 1:1. ICON: a clenched fist gripping a short iron bar.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="26" t="inlineStr">
         <is>
           <t>p3_strength.png</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3399,25 +3409,25 @@
       <c r="M44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>C-p3-agility</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="26" t="n">
         <v>53102</v>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>a leaping hare mid-stride</t>
         </is>
@@ -3427,27 +3437,27 @@
           <t>Aspect ratio 1:1. ICON: a leaping hare mid-stride.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>p3_agility.png</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3464,25 +3474,25 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>C-p3-endurance</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="26" t="n">
         <v>53103</v>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>a heavy wooden ox yoke</t>
         </is>
@@ -3492,27 +3502,27 @@
           <t>Aspect ratio 1:1. ICON: a heavy wooden ox yoke.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="26" t="inlineStr">
         <is>
           <t>p3_endurance.png</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3529,25 +3539,25 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>C-p3-intellect</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="26" t="n">
         <v>53104</v>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>an open ledger with a reed pen across it (no writing, only lines)</t>
         </is>
@@ -3557,27 +3567,27 @@
           <t>Aspect ratio 1:1. ICON: an open ledger with a reed pen across it (no writing, only lines).</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>p3_intellect.png</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3594,25 +3604,25 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>C-p3-perception</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="26" t="n">
         <v>53105</v>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>a single wide-open eye with a small hawk feather beside it</t>
         </is>
@@ -3622,27 +3632,27 @@
           <t>Aspect ratio 1:1. ICON: a single wide-open eye with a small hawk feather beside it.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>p3_perception.png</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3655,25 +3665,25 @@
       <c r="M48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>C-p3-charisma</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="26" t="n">
         <v>53106</v>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>two hands clasped in a handshake</t>
         </is>
@@ -3683,27 +3693,27 @@
           <t>Aspect ratio 1:1. ICON: two hands clasped in a handshake.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>p3_charisma.png</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3716,25 +3726,25 @@
       <c r="M49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
         <is>
           <t>C-p3-wisdom</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="26" t="n">
         <v>53107</v>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>an old oil lamp with a small flame</t>
         </is>
@@ -3744,27 +3754,27 @@
           <t>Aspect ratio 1:1. ICON: an old oil lamp with a small flame.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>p3_wisdom.png</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3777,25 +3787,25 @@
       <c r="M50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C1 - statlar (P3))</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>C-p3-faith</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="26" t="n">
         <v>53108</v>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>a knotted cord tied around a small standing stone</t>
         </is>
@@ -3805,27 +3815,27 @@
           <t>Aspect ratio 1:1. ICON: a knotted cord tied around a small standing stone.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>p3_faith.png</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3838,25 +3848,25 @@
       <c r="M51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>C-p5-guard</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="26" t="n">
         <v>53201</v>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>a round wooden shield with an iron boss, a spear behind it</t>
         </is>
@@ -3866,27 +3876,27 @@
           <t>Aspect ratio 1:1. ICON: a round wooden shield with an iron boss, a spear behind it.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>p5_guard.png</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3899,25 +3909,25 @@
       <c r="M52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
         <is>
           <t>C-p5-scout</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="26" t="n">
         <v>53202</v>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>a hawk perched on a gloved fist</t>
         </is>
@@ -3927,27 +3937,27 @@
           <t>Aspect ratio 1:1. ICON: a hawk perched on a gloved fist.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="26" t="inlineStr">
         <is>
           <t>p5_scout.png</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3964,25 +3974,25 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="26" t="inlineStr">
         <is>
           <t>C-p5-quartermaster</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="26" t="n">
         <v>53203</v>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>a tied grain sack with a wooden scoop</t>
         </is>
@@ -3992,27 +4002,27 @@
           <t>Aspect ratio 1:1. ICON: a tied grain sack with a wooden scoop.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="26" t="inlineStr">
         <is>
           <t>p5_quartermaster.png</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="H54" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4025,25 +4035,25 @@
       <c r="M54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>C-p5-wagoner</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="26" t="n">
         <v>53204</v>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>a spoked wooden cart wheel with a driving whip</t>
         </is>
@@ -4053,27 +4063,27 @@
           <t>Aspect ratio 1:1. ICON: a spoked wooden cart wheel with a driving whip.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="26" t="inlineStr">
         <is>
           <t>p5_wagoner.png</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4086,25 +4096,25 @@
       <c r="M55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>C-p5-crier</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="26" t="n">
         <v>53205</v>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>a brass hand bell</t>
         </is>
@@ -4114,27 +4124,27 @@
           <t>Aspect ratio 1:1. ICON: a brass hand bell.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="26" t="inlineStr">
         <is>
           <t>p5_crier.png</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4147,25 +4157,25 @@
       <c r="M56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C2 - gorevler (P5))</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="26" t="inlineStr">
         <is>
           <t>C-p5-herbalist</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="26" t="n">
         <v>53206</v>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>a mortar and pestle with a sprig of herbs</t>
         </is>
@@ -4175,27 +4185,27 @@
           <t>Aspect ratio 1:1. ICON: a mortar and pestle with a sprig of herbs.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="26" t="inlineStr">
         <is>
           <t>p5_herbalist.png</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4208,25 +4218,25 @@
       <c r="M57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C3 - kirginlik (P4))</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="26" t="inlineStr">
         <is>
           <t>C-p4-unfed</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="26" t="n">
         <v>53301</v>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>an empty wooden bowl tipped on its side, a spoon beside it</t>
         </is>
@@ -4236,27 +4246,27 @@
           <t>Aspect ratio 1:1. ICON: an empty wooden bowl tipped on its side, a spoon beside it.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="26" t="inlineStr">
         <is>
           <t>p4_unfed.png</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4269,25 +4279,25 @@
       <c r="M58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C3 - kirginlik (P4))</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="26" t="inlineStr">
         <is>
           <t>C-p4-benched</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="26" t="n">
         <v>53302</v>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>a sword lying unused on the ground beside a sheathed scabbard</t>
         </is>
@@ -4297,27 +4307,27 @@
           <t>Aspect ratio 1:1. ICON: a sword lying unused on the ground beside a sheathed scabbard.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="26" t="inlineStr">
         <is>
           <t>p4_benched.png</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4330,25 +4340,25 @@
       <c r="M59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C3 - kirginlik (P4))</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="26" t="inlineStr">
         <is>
           <t>C-p4-witnessed</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="26" t="n">
         <v>53303</v>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>a closed eye with a single dark tear</t>
         </is>
@@ -4358,27 +4368,27 @@
           <t>Aspect ratio 1:1. ICON: a closed eye with a single dark tear.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="26" t="inlineStr">
         <is>
           <t>p4_witnessed_death.png</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="H60" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4395,25 +4405,25 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C3 - kirginlik (P4))</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="26" t="inlineStr">
         <is>
           <t>C-p4-passed-over</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="26" t="n">
         <v>53304</v>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="26" t="inlineStr">
         <is>
           <t>a leader's staff lying broken in two</t>
         </is>
@@ -4423,27 +4433,27 @@
           <t>Aspect ratio 1:1. ICON: a leader's staff lying broken in two.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="26" t="inlineStr">
         <is>
           <t>p4_passed_over.png</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4460,25 +4470,25 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C4 - siniflar (K6))</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="26" t="inlineStr">
         <is>
           <t>C-k6-guard</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="26" t="n">
         <v>53401</v>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>a tall infantry shield planted upright</t>
         </is>
@@ -4488,27 +4498,27 @@
           <t>Aspect ratio 1:1. ICON: a tall infantry shield planted upright.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="26" t="inlineStr">
         <is>
           <t>k6a_guard.png</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="H62" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4521,25 +4531,25 @@
       <c r="M62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C4 - siniflar (K6))</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>C-k6-hunter</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="26" t="n">
         <v>53402</v>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="26" t="inlineStr">
         <is>
           <t>a recurved short bow with one arrow nocked</t>
         </is>
@@ -4549,27 +4559,27 @@
           <t>Aspect ratio 1:1. ICON: a recurved short bow with one arrow nocked.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="26" t="inlineStr">
         <is>
           <t>k6b_hunter.png</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4582,25 +4592,25 @@
       <c r="M63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C4 - siniflar (K6))</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
         <is>
           <t>C-k6-breaker</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="26" t="n">
         <v>53403</v>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>a heavy war hammer with a cracked iron plate</t>
         </is>
@@ -4610,27 +4620,27 @@
           <t>Aspect ratio 1:1. ICON: a heavy war hammer with a cracked iron plate.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="26" t="inlineStr">
         <is>
           <t>k6c_breaker.png</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="H64" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4643,25 +4653,25 @@
       <c r="M64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C4 - siniflar (K6))</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="26" t="inlineStr">
         <is>
           <t>C-k6-clerk</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="26" t="n">
         <v>53404</v>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="26" t="inlineStr">
         <is>
           <t>a rolled document tied with a cord and a wax seal</t>
         </is>
@@ -4671,27 +4681,27 @@
           <t>Aspect ratio 1:1. ICON: a rolled document tied with a cord and a wax seal.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="26" t="inlineStr">
         <is>
           <t>k6d_clerk.png</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4704,25 +4714,25 @@
       <c r="M65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="26" t="inlineStr">
         <is>
           <t>C-p2-virtue</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="26" t="n">
         <v>53501</v>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>a small upright flame in pale gold</t>
         </is>
@@ -4732,27 +4742,27 @@
           <t>Aspect ratio 1:1. ICON: a small upright flame in pale gold.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="26" t="inlineStr">
         <is>
           <t>p2_virtue.png</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="H66" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4765,25 +4775,25 @@
       <c r="M66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="26" t="inlineStr">
         <is>
           <t>C-p2-affliction</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="26" t="n">
         <v>53502</v>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="26" t="inlineStr">
         <is>
           <t>a cracked clay jar leaking dark liquid</t>
         </is>
@@ -4793,27 +4803,27 @@
           <t>Aspect ratio 1:1. ICON: a cracked clay jar leaking dark liquid.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="26" t="inlineStr">
         <is>
           <t>p2_affliction.png</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="H67" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4826,25 +4836,25 @@
       <c r="M67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="26" t="inlineStr">
         <is>
           <t>C-k4-bleed</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="26" t="n">
         <v>53503</v>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>three falling drops of dried-blood red</t>
         </is>
@@ -4854,27 +4864,27 @@
           <t>Aspect ratio 1:1. ICON: three falling drops of dried-blood red.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="26" t="inlineStr">
         <is>
           <t>k4a_bleed.png</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="H68" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4891,25 +4901,25 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
         <is>
           <t>C-k4-blight</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="26" t="n">
         <v>53504</v>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="26" t="inlineStr">
         <is>
           <t>a withered moss-green leaf with dark spots</t>
         </is>
@@ -4919,27 +4929,27 @@
           <t>Aspect ratio 1:1. ICON: a withered moss-green leaf with dark spots.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="26" t="inlineStr">
         <is>
           <t>k4b_blight.png</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="H69" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4952,25 +4962,25 @@
       <c r="M69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
         <is>
           <t>C-k4-stun</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D70" s="26" t="n">
         <v>53505</v>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>a small cluster of pale stars spinning around a dot</t>
         </is>
@@ -4980,27 +4990,27 @@
           <t>Aspect ratio 1:1. ICON: a small cluster of pale stars spinning around a dot.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="26" t="inlineStr">
         <is>
           <t>k4c_stun.png</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="H70" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K70" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5013,25 +5023,25 @@
       <c r="M70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="26" t="inlineStr">
         <is>
           <t>C-k4-stun-resist</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="26" t="n">
         <v>53506</v>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>an iron helmet with a small dent</t>
         </is>
@@ -5041,27 +5051,27 @@
           <t>Aspect ratio 1:1. ICON: an iron helmet with a small dent.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="26" t="inlineStr">
         <is>
           <t>k4d_stun_resist.png</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K71" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5074,25 +5084,25 @@
       <c r="M71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="26" t="inlineStr">
         <is>
           <t>C-k4-buff</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D72" s="26" t="n">
         <v>53507</v>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>an arrow pointing up, pale gold</t>
         </is>
@@ -5102,27 +5112,27 @@
           <t>Aspect ratio 1:1. ICON: an arrow pointing up, pale gold.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="26" t="inlineStr">
         <is>
           <t>k4e_buff.png</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="H72" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K72" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5135,25 +5145,25 @@
       <c r="M72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C5 - huylar ve savas durumlari (P2, K4))</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="26" t="inlineStr">
         <is>
           <t>C-k4-debuff</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="26" t="n">
         <v>53508</v>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="26" t="inlineStr">
         <is>
           <t>an arrow pointing down, dried-blood red</t>
         </is>
@@ -5163,27 +5173,27 @@
           <t>Aspect ratio 1:1. ICON: an arrow pointing down, dried-blood red.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="26" t="inlineStr">
         <is>
           <t>k4f_debuff.png</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="H73" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K73" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5196,25 +5206,25 @@
       <c r="M73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
         <is>
           <t>C-item-provisions</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="26" t="n">
         <v>53601</v>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="26" t="inlineStr">
         <is>
           <t>a bundle of flatbread and dried meat tied in cloth</t>
         </is>
@@ -5224,27 +5234,27 @@
           <t>Aspect ratio 1:1. ICON: a bundle of flatbread and dried meat tied in cloth.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="26" t="inlineStr">
         <is>
           <t>item_provisions.png</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="H74" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K74" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5257,25 +5267,25 @@
       <c r="M74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
         <is>
           <t>C-item-grain</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="26" t="n">
         <v>53602</v>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="26" t="inlineStr">
         <is>
           <t>an open sack of wheat grain</t>
         </is>
@@ -5285,27 +5295,27 @@
           <t>Aspect ratio 1:1. ICON: an open sack of wheat grain.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="26" t="inlineStr">
         <is>
           <t>item_grain.png</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="H75" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5322,25 +5332,25 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="26" t="inlineStr">
         <is>
           <t>C-item-cloth</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="26" t="n">
         <v>53603</v>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="26" t="inlineStr">
         <is>
           <t>a rolled bolt of woven cloth</t>
         </is>
@@ -5350,27 +5360,27 @@
           <t>Aspect ratio 1:1. ICON: a rolled bolt of woven cloth.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="26" t="inlineStr">
         <is>
           <t>item_cloth.png</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="H76" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5383,25 +5393,25 @@
       <c r="M76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>C-item-iron</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="26" t="n">
         <v>53604</v>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>three rough iron ingots stacked (the good is "Iron")</t>
         </is>
@@ -5411,27 +5421,27 @@
           <t>Aspect ratio 1:1. ICON: three rough iron ingots stacked (the good is "Iron").</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="26" t="inlineStr">
         <is>
           <t>item_weapon.png</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="H77" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5444,25 +5454,25 @@
       <c r="M77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
         <is>
           <t>C-item-potion</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="26" t="n">
         <v>53605</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="26" t="inlineStr">
         <is>
           <t>a small corked clay flask with a herb tag</t>
         </is>
@@ -5472,27 +5482,27 @@
           <t>Aspect ratio 1:1. ICON: a small corked clay flask with a herb tag.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="26" t="inlineStr">
         <is>
           <t>item_potion.png</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="H78" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J78" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5505,25 +5515,25 @@
       <c r="M78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
         <is>
           <t>C-item-furs</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="26" t="n">
         <v>53606</v>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="26" t="inlineStr">
         <is>
           <t>a folded stack of furs</t>
         </is>
@@ -5533,27 +5543,27 @@
           <t>Aspect ratio 1:1. ICON: a folded stack of furs.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="26" t="inlineStr">
         <is>
           <t>item_furs.png</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="H79" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5566,25 +5576,25 @@
       <c r="M79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>C-item-bandage</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="26" t="n">
         <v>53607</v>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="26" t="inlineStr">
         <is>
           <t>a rolled linen bandage</t>
         </is>
@@ -5594,27 +5604,27 @@
           <t>Aspect ratio 1:1. ICON: a rolled linen bandage.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="26" t="inlineStr">
         <is>
           <t>item_bandage.png</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="H80" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J80" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5627,25 +5637,25 @@
       <c r="M80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="26" t="inlineStr">
         <is>
           <t>C-item-spice</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="26" t="n">
         <v>53608</v>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="26" t="inlineStr">
         <is>
           <t>a small cloth pouch spilling red-brown spice</t>
         </is>
@@ -5655,27 +5665,27 @@
           <t>Aspect ratio 1:1. ICON: a small cloth pouch spilling red-brown spice.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="26" t="inlineStr">
         <is>
           <t>item_spice.png</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="H81" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5688,25 +5698,25 @@
       <c r="M81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="26" t="inlineStr">
         <is>
           <t>C-item-honey</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D82" s="26" t="n">
         <v>53609</v>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="26" t="inlineStr">
         <is>
           <t>a clay honey pot with a wooden dipper</t>
         </is>
@@ -5716,27 +5726,27 @@
           <t>Aspect ratio 1:1. ICON: a clay honey pot with a wooden dipper.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="26" t="inlineStr">
         <is>
           <t>item_honey.png</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="H82" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5749,25 +5759,25 @@
       <c r="M82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="26" t="inlineStr">
         <is>
           <t>C-item-silk</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="26" t="n">
         <v>53610</v>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="26" t="inlineStr">
         <is>
           <t>a folded length of shining (but muted) silk</t>
         </is>
@@ -5777,27 +5787,27 @@
           <t>Aspect ratio 1:1. ICON: a folded length of shining (but muted) silk.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="26" t="inlineStr">
         <is>
           <t>item_silk.png</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J83" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5810,25 +5820,25 @@
       <c r="M83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="26" t="inlineStr">
         <is>
           <t>C-item-jewelry</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D84" s="26" t="n">
         <v>53611</v>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="26" t="inlineStr">
         <is>
           <t>a small open wooden box with a bronze bracelet</t>
         </is>
@@ -5838,27 +5848,27 @@
           <t>Aspect ratio 1:1. ICON: a small open wooden box with a bronze bracelet.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="26" t="inlineStr">
         <is>
           <t>item_jewelry.png</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="H84" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J84" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5871,25 +5881,25 @@
       <c r="M84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="26" t="inlineStr">
         <is>
           <t>C-item-fish</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="26" t="n">
         <v>53612</v>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="26" t="inlineStr">
         <is>
           <t>two dried fish tied on a string</t>
         </is>
@@ -5899,27 +5909,27 @@
           <t>Aspect ratio 1:1. ICON: two dried fish tied on a string.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="26" t="inlineStr">
         <is>
           <t>item_fish.png</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="H85" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5932,25 +5942,25 @@
       <c r="M85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C6 - mallar (item ikonlari))</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="26" t="inlineStr">
         <is>
           <t>C-item-wine</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="26" t="n">
         <v>53613</v>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="26" t="inlineStr">
         <is>
           <t>a small wooden wine cask</t>
         </is>
@@ -5960,27 +5970,27 @@
           <t>Aspect ratio 1:1. ICON: a small wooden wine cask.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="26" t="inlineStr">
         <is>
           <t>item_wine.png</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J86" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K86" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5993,25 +6003,25 @@
       <c r="M86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="26" t="inlineStr">
         <is>
           <t>C-eq-weapon-1</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="26" t="n">
         <v>53701</v>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="26" t="inlineStr">
         <is>
           <t>plain iron arming sword, diagonal</t>
         </is>
@@ -6021,27 +6031,27 @@
           <t>Aspect ratio 1:1. ICON: plain iron arming sword, diagonal.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="26" t="inlineStr">
         <is>
           <t>eq_weapon_tier_1.png</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="H87" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J87" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6054,25 +6064,25 @@
       <c r="M87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="26" t="inlineStr">
         <is>
           <t>C-eq-weapon-2</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="26" t="n">
         <v>53702</v>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="26" t="inlineStr">
         <is>
           <t>curved sabre with brass pommel cap, diagonal</t>
         </is>
@@ -6082,27 +6092,27 @@
           <t>Aspect ratio 1:1. ICON: curved sabre with brass pommel cap, diagonal.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="26" t="inlineStr">
         <is>
           <t>eq_weapon_tier_2.png</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="H88" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J88" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6115,25 +6125,25 @@
       <c r="M88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="26" t="inlineStr">
         <is>
           <t>C-eq-weapon-3</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="26" t="n">
         <v>53703</v>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="26" t="inlineStr">
         <is>
           <t>curved sabre with falcon-wing guard, diagonal</t>
         </is>
@@ -6143,27 +6153,27 @@
           <t>Aspect ratio 1:1. ICON: curved sabre with falcon-wing guard, diagonal.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="26" t="inlineStr">
         <is>
           <t>eq_weapon_tier_3.png</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="H89" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J89" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6176,25 +6186,25 @@
       <c r="M89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="26" t="inlineStr">
         <is>
           <t>C-eq-armor-1</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="26" t="n">
         <v>53704</v>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="26" t="inlineStr">
         <is>
           <t>boiled-leather cuirass, front view</t>
         </is>
@@ -6204,27 +6214,27 @@
           <t>Aspect ratio 1:1. ICON: boiled-leather cuirass, front view.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="26" t="inlineStr">
         <is>
           <t>eq_armor_tier_1.png</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="H90" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J90" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6237,25 +6247,25 @@
       <c r="M90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" s="26" t="inlineStr">
         <is>
           <t>C-eq-armor-2</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="26" t="n">
         <v>53705</v>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="26" t="inlineStr">
         <is>
           <t>mail shirt, front view</t>
         </is>
@@ -6265,27 +6275,27 @@
           <t>Aspect ratio 1:1. ICON: mail shirt, front view.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="26" t="inlineStr">
         <is>
           <t>eq_armor_tier_2.png</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="H91" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J91" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K91" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6298,25 +6308,25 @@
       <c r="M91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="26" t="inlineStr">
         <is>
           <t>C-eq-armor-3</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D92" s="26" t="n">
         <v>53706</v>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="26" t="inlineStr">
         <is>
           <t>lamellar cuirass with pauldrons, front view</t>
         </is>
@@ -6326,27 +6336,27 @@
           <t>Aspect ratio 1:1. ICON: lamellar cuirass with pauldrons, front view.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="26" t="inlineStr">
         <is>
           <t>eq_armor_tier_3.png</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="H92" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J92" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K92" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6359,25 +6369,25 @@
       <c r="M92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
         <is>
           <t>C-eq-ring-marksman</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="26" t="n">
         <v>53707</v>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="26" t="inlineStr">
         <is>
           <t>an iron archer's thumb ring</t>
         </is>
@@ -6387,27 +6397,27 @@
           <t>Aspect ratio 1:1. ICON: an iron archer's thumb ring.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="26" t="inlineStr">
         <is>
           <t>eq_ring_marksman.png</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="H93" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K93" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6420,25 +6430,25 @@
       <c r="M93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="26" t="inlineStr">
         <is>
           <t>C-eq-ring-gambler</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D94" s="26" t="n">
         <v>53708</v>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="26" t="inlineStr">
         <is>
           <t>a bronze ring set with a small bone die</t>
         </is>
@@ -6448,27 +6458,27 @@
           <t>Aspect ratio 1:1. ICON: a bronze ring set with a small bone die.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="26" t="inlineStr">
         <is>
           <t>eq_ring_gambler.png</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="H94" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J94" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6481,25 +6491,25 @@
       <c r="M94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="26" t="inlineStr">
         <is>
           <t>C-eq-ring-charmed</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="26" t="n">
         <v>53709</v>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="26" t="inlineStr">
         <is>
           <t>a ring of twisted copper wire with a blue bead</t>
         </is>
@@ -6509,27 +6519,27 @@
           <t>Aspect ratio 1:1. ICON: a ring of twisted copper wire with a blue bead.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="26" t="inlineStr">
         <is>
           <t>eq_ring_charmed.png</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="H95" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J95" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6546,25 +6556,25 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="26" t="inlineStr">
         <is>
           <t>C-eq-amulet-ward</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
+      <c r="D96" s="26" t="n">
         <v>53710</v>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="26" t="inlineStr">
         <is>
           <t>a triangular red cloth charm on a cord</t>
         </is>
@@ -6574,27 +6584,27 @@
           <t>Aspect ratio 1:1. ICON: a triangular red cloth charm on a cord.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="26" t="inlineStr">
         <is>
           <t>eq_amulet_ward.png</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="H96" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K96" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6607,25 +6617,25 @@
       <c r="M96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="26" t="inlineStr">
         <is>
           <t>C-eq-amulet-fang</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="26" t="n">
         <v>53711</v>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="26" t="inlineStr">
         <is>
           <t>a wolf fang on a leather thong</t>
         </is>
@@ -6635,27 +6645,27 @@
           <t>Aspect ratio 1:1. ICON: a wolf fang on a leather thong.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="26" t="inlineStr">
         <is>
           <t>eq_amulet_wolf_fang.png</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="H97" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J97" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K97" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6668,25 +6678,25 @@
       <c r="M97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="26" t="inlineStr">
         <is>
           <t>Ikon aileleri (C7 - ekipman ikonlari (yeni))</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="26" t="inlineStr">
         <is>
           <t>C-eq-amulet-courage</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D98" s="26" t="n">
         <v>53712</v>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="26" t="inlineStr">
         <is>
           <t>a hammered bronze disc pendant</t>
         </is>
@@ -6696,27 +6706,27 @@
           <t>Aspect ratio 1:1. ICON: a hammered bronze disc pendant.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="26" t="inlineStr">
         <is>
           <t>eq_amulet_courage.png</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="H98" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J98" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K98" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6729,25 +6739,25 @@
       <c r="M98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="26" t="inlineStr">
         <is>
           <t>D-b1</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="26" t="n">
         <v>54101</v>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="26" t="inlineStr">
         <is>
           <t>guild</t>
         </is>
@@ -6758,27 +6768,27 @@
 SCENE: A merchants' guild clerk's desk: open account ledger at the left edge, a candle, an inkwell with a reed pen, a red wax seal and a stick of sealing wax, a small stack of worn coins and a folded contract with a seal at the right edge.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="26" t="inlineStr">
         <is>
           <t>b1_guild.jpg</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="H99" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J99" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6791,25 +6801,25 @@
       <c r="M99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="26" t="inlineStr">
         <is>
           <t>D-b2</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D100" s="26" t="n">
         <v>54102</v>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="26" t="inlineStr">
         <is>
           <t>market</t>
         </is>
@@ -6820,27 +6830,27 @@
 SCENE: A market stall counter: brass balance scales at the left edge, open sacks of grain and spice, a clay jar, a bolt of cloth and a basket of dried fish at the right edge, coins scattered on the bottom edge.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="26" t="inlineStr">
         <is>
           <t>b2_market.jpg</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="H100" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J100" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6853,25 +6863,25 @@
       <c r="M100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="26" t="inlineStr">
         <is>
           <t>D-b3</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="26" t="n">
         <v>54103</v>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" s="26" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
@@ -6882,27 +6892,27 @@
 SCENE: A tavern table at night: pewter mugs and a clay jug at the left edge, a torn hand-drawn route map (no writing) and a dagger stuck in the wood at the right edge, candle stubs, spilled drink rings.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="26" t="inlineStr">
         <is>
           <t>b3_tavern.jpg</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="H101" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J101" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K101" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6915,25 +6925,25 @@
       <c r="M101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="26" t="inlineStr">
         <is>
           <t>D-b4</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
+      <c r="D102" s="26" t="n">
         <v>54104</v>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="26" t="inlineStr">
         <is>
           <t>caravan yard</t>
         </is>
@@ -6944,27 +6954,27 @@
 SCENE: A wagon yard workbench: an iron horseshoe, a coil of rope and a mallet at the left edge, a spoked cart wheel leaning at the right edge, wood shavings, a pot of axle grease.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="26" t="inlineStr">
         <is>
           <t>b4_yard.jpg</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="H102" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6977,25 +6987,25 @@
       <c r="M102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="26" t="inlineStr">
         <is>
           <t>D-b5</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="26" t="n">
         <v>54105</v>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" s="26" t="inlineStr">
         <is>
           <t>church</t>
         </is>
@@ -7006,27 +7016,27 @@
 SCENE: A quiet stone hall's lectern: a bowl of water with floating petals at the left edge, bundles of dried herbs and a tall candle at the right edge, knotted cords; no religious symbols.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="26" t="inlineStr">
         <is>
           <t>b5_church.jpg</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="H103" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J103" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7039,25 +7049,25 @@
       <c r="M103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" s="26" t="inlineStr">
         <is>
           <t>D-b7</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D104" s="26" t="n">
         <v>54106</v>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" s="26" t="inlineStr">
         <is>
           <t>planner</t>
         </is>
@@ -7068,27 +7078,27 @@
 SCENE: A caravan master's planning table: a large rolled-out parchment map (no writing) under brass weights at the left edge, a compass-like sundial, a provision list of ink strokes, a lantern at the right edge.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="26" t="inlineStr">
         <is>
           <t>b7_planner.jpg</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="H104" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J104" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K104" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7101,25 +7111,25 @@
       <c r="M104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="26" t="inlineStr">
         <is>
           <t>D-b8</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D105" s="26" t="n">
         <v>54107</v>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="26" t="inlineStr">
         <is>
           <t>recruitment</t>
         </is>
@@ -7130,27 +7140,27 @@
 SCENE: A hiring board in a square: a rough wooden table with a stack of worn tokens, a purse, a walking staff leaning at the right edge, the edge of a crowd's cloaks at the left edge.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" s="26" t="inlineStr">
         <is>
           <t>b8_recruit.jpg</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="H105" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J105" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K105" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7163,25 +7173,25 @@
       <c r="M105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" s="26" t="inlineStr">
         <is>
           <t>D-b9</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D106" s="26" t="n">
         <v>54108</v>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E106" s="26" t="inlineStr">
         <is>
           <t>tent</t>
         </is>
@@ -7192,27 +7202,27 @@
 SCENE: Inside a road tent at night: a bedroll and a saddlebag at the left edge, an oil lamp and a small travel chest at the right edge, canvas walls in dark tan, the centre a dark rug.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="26" t="inlineStr">
         <is>
           <t>b9_tent.jpg</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="H106" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J106" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K106" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7225,25 +7235,25 @@
       <c r="M106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" s="26" t="inlineStr">
         <is>
           <t>D-b10</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D107" s="26" t="n">
         <v>54109</v>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" s="26" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -7254,27 +7264,27 @@
 SCENE: A city notary's desk with the window open onto a walled trade town at dusk (walls, gate, warehouses, no religious buildings) at the left edge, keys and a seal at the right edge.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="26" t="inlineStr">
         <is>
           <t>b10_city.jpg</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="H107" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J107" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K107" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7287,25 +7297,25 @@
       <c r="M107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="26" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="26" t="inlineStr">
         <is>
           <t>Yonetim ekrani arka planlari (Management screen backgrounds)</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" s="26" t="inlineStr">
         <is>
           <t>D-l1</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D108" s="26" t="n">
         <v>54110</v>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" s="26" t="inlineStr">
         <is>
           <t>ledger</t>
         </is>
@@ -7316,27 +7326,27 @@
 SCENE: An open old account book seen from directly above, filling the frame: two yellowed ruled pages with indistinct ink strokes only, a ribbon marker, stains and a candle-wax drip.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="26" t="inlineStr">
         <is>
           <t>l1_ledger.jpg</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="H108" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="26" t="inlineStr">
         <is>
           <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J108" s="26" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7349,25 +7359,25 @@
       <c r="M108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="26" t="inlineStr">
         <is>
           <t>E-g9</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
+      <c r="D109" s="26" t="n">
         <v>55101</v>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="26" t="inlineStr">
         <is>
           <t>seal</t>
         </is>
@@ -7378,27 +7388,27 @@
 PROP: A round dried-blood red wax seal pressed onto nothing, its face stamped with a simple caravan wheel (no letters), slightly uneven edge, a short cut ribbon under it.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" s="26" t="inlineStr">
         <is>
           <t>g9_seal.png</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="H109" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J109" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K109" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7411,25 +7421,25 @@
       <c r="M109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="26" t="inlineStr">
         <is>
           <t>E-g9b</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D110" s="26" t="n">
         <v>55102</v>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" s="26" t="inlineStr">
         <is>
           <t>cracked seal</t>
         </is>
@@ -7440,27 +7450,27 @@
 PROP: The exact same wax seal as before, now cracked through the middle into two pieces with a chip missing. (Same thread as E-g9, say "the same seal".)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="26" t="inlineStr">
         <is>
           <t>g9b_seal_cracked.png</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="H110" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J110" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K110" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7473,25 +7483,25 @@
       <c r="M110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="26" t="inlineStr">
         <is>
           <t>E-c1</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D111" s="26" t="n">
         <v>55103</v>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E111" s="26" t="inlineStr">
         <is>
           <t>mourning crepe</t>
         </is>
@@ -7502,27 +7512,27 @@
 PROP: A black mourning crepe ribbon tied in a simple bow, frayed tails hanging down.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" s="26" t="inlineStr">
         <is>
           <t>c1_crepe.png</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="H111" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J111" s="26" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K111" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7535,25 +7545,25 @@
       <c r="M111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="26" t="inlineStr">
         <is>
           <t>E-l2</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D112" s="26" t="n">
         <v>55104</v>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="26" t="inlineStr">
         <is>
           <t>ribbon</t>
         </is>
@@ -7564,27 +7574,27 @@
 PROP: A long faded dried-blood red silk bookmark ribbon hanging straight down, forked tail at the bottom.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="26" t="inlineStr">
         <is>
           <t>l2_ribbon.png</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="H112" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J112" s="26" t="inlineStr">
         <is>
           <t>1:4 (uzun)</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7597,25 +7607,25 @@
       <c r="M112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="26" t="inlineStr">
         <is>
           <t>E-r9</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D113" s="26" t="n">
         <v>55105</v>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="26" t="inlineStr">
         <is>
           <t>strike</t>
         </is>
@@ -7626,27 +7636,27 @@
 PROP: A single horizontal stroke of dark ink made with a reed pen, thick in the middle and tapering at both ends, a few spatters.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="26" t="inlineStr">
         <is>
           <t>r9_strike.png</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="H113" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J113" s="26" t="inlineStr">
         <is>
           <t>4:1 (genis)</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7659,25 +7669,25 @@
       <c r="M113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="26" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="26" t="inlineStr">
         <is>
           <t>Bagimsiz nesneler (Standalone props)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="26" t="inlineStr">
         <is>
           <t>E-b6</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D114" s="26" t="n">
         <v>55106</v>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="26" t="inlineStr">
         <is>
           <t>map</t>
         </is>
@@ -7688,27 +7698,27 @@
 PROP: A torn parchment page with a hand-drawn regional map: five small walled towns joined by roads, mountains, a forest, a river running to a coast — no writing, no labels, no compass letters. Torn, irregular edges.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="26" t="inlineStr">
         <is>
           <t>b6_map.png</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="H114" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="26" t="inlineStr">
         <is>
           <t>EVET - PNG (yirtik kenar kalir, sadece cevresi seffaflasir)</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="26" t="inlineStr">
         <is>
           <t>4:3</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K114" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7721,25 +7731,25 @@
       <c r="M114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" s="26" t="inlineStr">
         <is>
           <t>Butun hayvanlar - iskelet pozunda (Whole animals in the rig pose)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="26" t="inlineStr">
         <is>
           <t>F-horse</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D115" s="26" t="n">
         <v>61101</v>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="26" t="inlineStr">
         <is>
           <t>Riding horse (saddled)</t>
         </is>
@@ -7752,27 +7762,27 @@
 Matte, worn, travelled - mud on the lower legs.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" s="26" t="inlineStr">
         <is>
           <t>horse.png</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H115" s="26" t="inlineStr">
         <is>
           <t>horse_pose_reference.jpg</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I115" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J115" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K115" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7789,25 +7799,25 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="26" t="inlineStr">
         <is>
           <t>Butun hayvanlar - iskelet pozunda (Whole animals in the rig pose)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="26" t="inlineStr">
         <is>
           <t>F-ox</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D116" s="26" t="n">
         <v>61102</v>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="26" t="inlineStr">
         <is>
           <t>Draught ox (yoked)</t>
         </is>
@@ -7820,27 +7830,27 @@
 Matte, dusty, tired working animal.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" s="26" t="inlineStr">
         <is>
           <t>ox.png</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H116" s="26" t="inlineStr">
         <is>
           <t>ox_pose_reference.jpg</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I116" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J116" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K116" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7857,25 +7867,25 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="26" t="inlineStr">
         <is>
           <t>Butun hayvanlar - iskelet pozunda (Whole animals in the rig pose)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="26" t="inlineStr">
         <is>
           <t>F-wolf</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D117" s="26" t="n">
         <v>61103</v>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="26" t="inlineStr">
         <is>
           <t>Steppe wolf</t>
         </is>
@@ -7887,27 +7897,27 @@
 Wild, hungry, dangerous - but not a monster: a real wolf.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="26" t="inlineStr">
         <is>
           <t>wolf.png</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H117" s="26" t="inlineStr">
         <is>
           <t>wolf_pose_reference.jpg</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I117" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J117" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K117" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7924,25 +7934,25 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="26" t="inlineStr">
         <is>
           <t>Butun hayvanlar - iskelet pozunda (Whole animals in the rig pose)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" s="26" t="inlineStr">
         <is>
           <t>F-bear</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D118" s="26" t="n">
         <v>61104</v>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" s="26" t="inlineStr">
         <is>
           <t>Brown bear</t>
         </is>
@@ -7954,27 +7964,27 @@
 Heavy, slow, overwhelming weight - the biggest animal in the game.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="26" t="inlineStr">
         <is>
           <t>bear.png</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H118" s="26" t="inlineStr">
         <is>
           <t>bear_pose_reference.jpg</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I118" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J118" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="K118" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7991,25 +8001,25 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="26" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="26" t="inlineStr">
         <is>
           <t>Butun hayvanlar - iskelet pozunda (Whole animals in the rig pose)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="26" t="inlineStr">
         <is>
           <t>F-boar</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D119" s="26" t="n">
         <v>61105</v>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="26" t="inlineStr">
         <is>
           <t>Wild boar</t>
         </is>
@@ -8021,27 +8031,27 @@
 Aggressive, compact, low to the ground.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="26" t="inlineStr">
         <is>
           <t>boar.png</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H119" s="26" t="inlineStr">
         <is>
           <t>boar_pose_reference.jpg</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I119" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J119" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8058,25 +8068,25 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="26" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="26" t="inlineStr">
         <is>
           <t>Parca sayfasi yedek yontemi - sadece F basarisiz olursa (Part-sheet fallback)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="26" t="inlineStr">
         <is>
           <t>G-horse</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D120" s="26" t="n">
         <v>61201</v>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="26" t="inlineStr">
         <is>
           <t>horse</t>
         </is>
@@ -8088,27 +8098,27 @@
 Paint the horse (F bolumundeki ayni turun ANIMAL paragrafini kullan) as separate pieces: in each cell, paint that part of the animal exactly over the grey mannequin, same position, scale and angle, lined up with its red and blue dots, about 10-15% longer at the red-dot end so joints overlap. Keep the image the same size and the grid the same layout. Flat mid-grey (RGB 140,140,140) background, no dots, no mannequin, no cell lines in the result. Style: STYLE-F'nin STYLE bolumu (bkz. F kategorisinin basindaki STYLE-F blogu).</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" s="26" t="inlineStr">
         <is>
           <t>horse_sheet.png</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H120" s="26" t="inlineStr">
         <is>
           <t>horse_sheet_template.png</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I120" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J120" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="K120" s="26" t="inlineStr">
         <is>
           <t>Sadece F kategorisindeki ilgili hayvan resmi basarisiz olursa kullanilir.</t>
         </is>
@@ -8125,25 +8135,25 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="26" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="26" t="inlineStr">
         <is>
           <t>Parca sayfasi yedek yontemi - sadece F basarisiz olursa (Part-sheet fallback)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="26" t="inlineStr">
         <is>
           <t>G-ox</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D121" s="26" t="n">
         <v>61202</v>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="26" t="inlineStr">
         <is>
           <t>ox</t>
         </is>
@@ -8155,27 +8165,27 @@
 Paint the ox (F bolumundeki ayni turun ANIMAL paragrafini kullan) as separate pieces: in each cell, paint that part of the animal exactly over the grey mannequin, same position, scale and angle, lined up with its red and blue dots, about 10-15% longer at the red-dot end so joints overlap. Keep the image the same size and the grid the same layout. Flat mid-grey (RGB 140,140,140) background, no dots, no mannequin, no cell lines in the result. Style: STYLE-F'nin STYLE bolumu (bkz. F kategorisinin basindaki STYLE-F blogu).</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="26" t="inlineStr">
         <is>
           <t>ox_sheet.png</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H121" s="26" t="inlineStr">
         <is>
           <t>ox_sheet_template.png</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I121" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J121" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K121" s="26" t="inlineStr">
         <is>
           <t>Sadece F kategorisindeki ilgili hayvan resmi basarisiz olursa kullanilir.</t>
         </is>
@@ -8192,25 +8202,25 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="26" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" s="26" t="inlineStr">
         <is>
           <t>Parca sayfasi yedek yontemi - sadece F basarisiz olursa (Part-sheet fallback)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="26" t="inlineStr">
         <is>
           <t>G-wolf</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n">
+      <c r="D122" s="26" t="n">
         <v>61203</v>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="26" t="inlineStr">
         <is>
           <t>wolf</t>
         </is>
@@ -8222,27 +8232,27 @@
 Paint the wolf (F bolumundeki ayni turun ANIMAL paragrafini kullan) as separate pieces: in each cell, paint that part of the animal exactly over the grey mannequin, same position, scale and angle, lined up with its red and blue dots, about 10-15% longer at the red-dot end so joints overlap. Keep the image the same size and the grid the same layout. Flat mid-grey (RGB 140,140,140) background, no dots, no mannequin, no cell lines in the result. Style: STYLE-F'nin STYLE bolumu (bkz. F kategorisinin basindaki STYLE-F blogu).</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="26" t="inlineStr">
         <is>
           <t>wolf_sheet.png</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H122" s="26" t="inlineStr">
         <is>
           <t>wolf_sheet_template.png</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="I122" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J122" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K122" s="26" t="inlineStr">
         <is>
           <t>Sadece F kategorisindeki ilgili hayvan resmi basarisiz olursa kullanilir.</t>
         </is>
@@ -8259,25 +8269,25 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="26" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" s="26" t="inlineStr">
         <is>
           <t>Parca sayfasi yedek yontemi - sadece F basarisiz olursa (Part-sheet fallback)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="26" t="inlineStr">
         <is>
           <t>G-bear</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D123" s="26" t="n">
         <v>61204</v>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" s="26" t="inlineStr">
         <is>
           <t>bear</t>
         </is>
@@ -8289,27 +8299,27 @@
 Paint the bear (F bolumundeki ayni turun ANIMAL paragrafini kullan) as separate pieces: in each cell, paint that part of the animal exactly over the grey mannequin, same position, scale and angle, lined up with its red and blue dots, about 10-15% longer at the red-dot end so joints overlap. Keep the image the same size and the grid the same layout. Flat mid-grey (RGB 140,140,140) background, no dots, no mannequin, no cell lines in the result. Style: STYLE-F'nin STYLE bolumu (bkz. F kategorisinin basindaki STYLE-F blogu).</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="26" t="inlineStr">
         <is>
           <t>bear_sheet.png</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H123" s="26" t="inlineStr">
         <is>
           <t>bear_sheet_template.png</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I123" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J123" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="K123" s="26" t="inlineStr">
         <is>
           <t>Sadece F kategorisindeki ilgili hayvan resmi basarisiz olursa kullanilir.</t>
         </is>
@@ -8326,25 +8336,25 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="26" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>Parca sayfasi yedek yontemi - sadece F basarisiz olursa (Part-sheet fallback)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="26" t="inlineStr">
         <is>
           <t>G-boar</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D124" s="26" t="n">
         <v>61205</v>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="26" t="inlineStr">
         <is>
           <t>boar</t>
         </is>
@@ -8356,27 +8366,27 @@
 Paint the boar (F bolumundeki ayni turun ANIMAL paragrafini kullan) as separate pieces: in each cell, paint that part of the animal exactly over the grey mannequin, same position, scale and angle, lined up with its red and blue dots, about 10-15% longer at the red-dot end so joints overlap. Keep the image the same size and the grid the same layout. Flat mid-grey (RGB 140,140,140) background, no dots, no mannequin, no cell lines in the result. Style: STYLE-F'nin STYLE bolumu (bkz. F kategorisinin basindaki STYLE-F blogu).</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="26" t="inlineStr">
         <is>
           <t>boar_sheet.png</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H124" s="26" t="inlineStr">
         <is>
           <t>boar_sheet_template.png</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="I124" s="26" t="inlineStr">
         <is>
           <t>EVET - arka planı kaldirilmis PNG (seffaf)</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J124" s="26" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K124" s="26" t="inlineStr">
         <is>
           <t>Sadece F kategorisindeki ilgili hayvan resmi basarisiz olursa kullanilir.</t>
         </is>
@@ -9591,4 +9601,1216 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Alt Grup</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Gorsel / Item Adi</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Prompt Metni (Ingilizce - Gemini'ye yapistirilacak)</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Cikti Dosya Adi</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Referans Gorsel Dosyasi</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>PNG Gerekli mi? (Arka Plan Kaldirma)</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>En-Boy Orani</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Notlar</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Denetim Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>B-a</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="n">
+        <v>41301</v>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>carcass_on_road</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A freshly killed deer carcass lying at the edge of a dirt road, teeth marks visible at its throat, a few dark scavenger birds circling low against a pale morning sky. No predator in sight, only the kill and its silence. Flattened grass around it, cold early light.
+AVOID: text, frame, close-up gore, exposed bone, blood pooling.</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>e6v_carcass.jpg</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K2" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_carcass_on_road</t>
+        </is>
+      </c>
+      <c r="L2" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>B-b</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>41302</v>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>fisher_catch</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A dirt caravan road crossing a shallow, fast-flowing river at a ford, sunlight glinting on the water, the silver flash of fish just beneath a ripple near the bank, a coiled fishing net resting on a flat stone at the water's edge. Midday light, reeds along the bank.
+AVOID: text, frame, people, boats.</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>e6w_fishing.jpg</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_culture_fisher_catch</t>
+        </is>
+      </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M3" s="25" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>B-c</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="n">
+        <v>41303</v>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>port_gossip</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: The dim common room of a small wayside inn, a traveling merchant leaning across a rough wooden table toward the viewer, speaking low, a half-full clay cup between them, packs and a coil of ship's rope against the wall behind him hinting at a long road from the coast. Warm lamplight, smoky air.
+AVOID: text, frame, detailed face, modern objects.</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>e6x_gossip.jpg</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K4" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_culture_port_gossip</t>
+        </is>
+      </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>B-d</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>41304</v>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>valley_dispute</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: Two merchants standing close beside a loaded cart, one jabbing a finger at an open ledger book held by the other, both mid-argument, loose parchment and a fallen wax seal scattered on a crate between them. Overcast daylight, tense posture.
+AVOID: text (including on the ledger pages), frame, detailed faces, violence.</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>e6y_ledger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_culture_valley_dispute</t>
+        </is>
+      </c>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>B-e</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>41305</v>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>forage</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A lush roadside verge thick with wild edible greens, dark berries on low bushes and a few mushrooms at the base of a tree, dew still on the leaves. An empty woven gathering basket rests in the grass. Soft early-morning light.
+AVOID: text, frame, people, poisonous-looking fungi.</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>e6z_forage.jpg</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K6" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_forage</t>
+        </is>
+      </c>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M6" s="25" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>B-f</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>41306</v>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>hunting_trip</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A broad-antlered stag standing alert among sunlit birch trees, ears forward, two or three does grazing a short distance behind it, dappled forest light, dry leaves and undergrowth in the foreground. A tense, watchful stillness.
+AVOID: text, frame, hunters, weapons, gore.</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>e6aa_stag.jpg</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_hunting_trip</t>
+        </is>
+      </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>B-g</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>41307</v>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>left_behind_return</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A weathered shepherd standing at the roadside with a small flock of sheep, leaning on a crook, looking toward the viewer as if about to speak, a cluster of low village rooftops visible on a distant hillside behind him. Late-afternoon light, dust on the road.
+AVOID: text, frame, detailed face.</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>e6ab_shepherd.jpg</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K8" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_left_behind_return</t>
+        </is>
+      </c>
+      <c r="L8" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>B-h</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>41308</v>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>military_convoy</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A column of armed soldiers marching along a wide road under a plain, unmarked banner, spears held upright in loose formation, an officer at the head raising one hand toward the viewer in a halt gesture. Open plains, midday light, dust rising from marching feet.
+AVOID: text, frame, heraldry or symbols on the banner, modern uniforms.</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>e6ac_convoy.jpg</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_military_convoy</t>
+        </is>
+      </c>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>B-i</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>41309</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>mutiny</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A small knot of merchants and hired hands huddled close around a low campfire at night, heads bent together in hushed conversation, one glancing warily over his shoulder toward the viewer as if just interrupted. Firelight and long shadows, a tense mood.
+AVOID: text, frame, detailed faces, weapons drawn.</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>e6ad_unrest.jpg</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_mutiny</t>
+        </is>
+      </c>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>B-j</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>41310</v>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>party_investigation</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A single figure standing apart from the rest of a camp at dusk, arms crossed defensively, lit from one side by a lantern held just out of frame, the caravan's own fire blurred in the background where the others watch from a distance. An uneasy, accusatory mood, no violence shown.
+AVOID: text, frame, detailed face, pointing fingers, violence.</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>e6ae_accusation.jpg</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_party_investigation</t>
+        </is>
+      </c>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>B-k</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>41311</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>party_theft</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A half-emptied travel pack lying open on a bedroll at a campsite at dawn, its contents disturbed and one strap cut, faint footprints leading away into the dry grass beyond the firelight's reach. No person in frame, only the aftermath.
+AVOID: text, frame, people, gore.</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>e6af_theft.jpg</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K12" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_party_theft</t>
+        </is>
+      </c>
+      <c r="L12" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>B-l</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>41312</v>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>profiteer_recognized</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A tired column of refugees paused on a dusty road, bundles and children among them, one gaunt figure at the front staring hard and accusingly straight at the viewer - recognition and resentment carried in the posture, not the face. Harsh midday light, dust haze.
+AVOID: text, frame, detailed face, violence.</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>e6ag_profiteer.jpg</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_profiteer_recognized</t>
+        </is>
+      </c>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>B-m</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>41313</v>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>refugee_column</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A weary column of refugees resting at the roadside, worn bundles and a couple of handcarts piled with belongings, thin children sitting listlessly in the dust beside an exhausted parent. Overcast light, an empty road stretching behind them.
+AVOID: text, frame, detailed faces, graphic suffering.</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>e6ah_refugees.jpg</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K14" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_refugee_column</t>
+        </is>
+      </c>
+      <c r="L14" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>B-n</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>41314</v>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>sick_merchant</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A merchant lying on a bedroll inside the open flap of a canvas-covered wagon, a damp cloth on his forehead, blankets pulled tight despite visible sweat, a half-empty waterskin and an untouched bowl beside him. Dim lamplight, a worried stillness.
+AVOID: text, frame, detailed face, medical gore.</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>e6ai_sick.jpg</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_sick_merchant</t>
+        </is>
+      </c>
+      <c r="L15" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M15" s="25" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>B-o</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>41315</v>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>spoiled_provisions</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: An open wooden supply crate with grain sacks pulled aside, revealing a dark patch of mold and rot at the bottom, a couple of flies hovering above it, the rest of the tidy stores stacked around it. Flat daylight inside a wagon's shade.
+AVOID: text, frame, people, excessive insects or gore.</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>e6aj_spoiled.jpg</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K16" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_spoiled_provisions</t>
+        </is>
+      </c>
+      <c r="L16" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>B-p</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>41316</v>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>stress_brawl</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: Two rough caravan hands mid-scuffle beside a campfire at night, one shoving the other back, a toppled stool and scattered firewood between them, onlookers' silhouettes half-turned toward the fight in the firelight. Chaotic motion, raised dust.
+AVOID: text, frame, detailed faces, blood, weapons.</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>e6ak_brawl.jpg</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_stress_brawl</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M17" s="25" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>B-q</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>41317</v>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>traveling_tinker</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A solitary traveling tinker walking along a dusty road, an enormous bundle of pots, tools and clattering metal wares strapped to his back and a walking staff in hand, raising a friendly half-wave toward the viewer. Warm afternoon light, open countryside behind him.
+AVOID: text, frame, detailed face.</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>e6al_tinker.jpg</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_traveling_tinker</t>
+        </is>
+      </c>
+      <c r="L18" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M18" s="25" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Olay karti illustrasyonlari - 2. tur (eksik 18 olay)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>B-r</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>41318</v>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>wanderer_revenge</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>SCENE: A gaunt but now well-armed man standing at the center of the road blocking the way, flanked by several rough companions with weapons, his cold, knowing stare aimed straight at the viewer suggesting old, unfinished business rather than a random ambush. Late-afternoon light, long shadows across the road.
+AVOID: text, frame, detailed faces, gore.</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>e6am_revenge.jpg</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>HAYIR - JPG, tam kadraj (arka plan kalir)</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>event_id: evt_wanderer_revenge</t>
+        </is>
+      </c>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="M19" s="25" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Denetim" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Yeniden Üretilecekler" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ozet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Olay Kartlari 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kalan Görsel İşler" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Denetim" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Yeniden Üretilecekler" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ozet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Olay Kartlari 2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Denetim'!$A$1:$M$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Yeniden Üretilecekler'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Denetim'!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yeniden Üretilecekler'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +60,18 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +113,16 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003F3A34"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE8DF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -186,6 +207,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,6 +583,2240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>Grup</t>
+        </is>
+      </c>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>Kalem</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Çıktı dosyası</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Yöntem</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Şablon / referans</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>İşleme komutu</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>Öncelik</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Fötr Şapka (hat_felt)</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>hat_felt/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; hat_felt</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-01. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Yolcu Kukuletesi (hat_hood)</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>hat_hood/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; hat_hood</t>
+        </is>
+      </c>
+      <c r="H3" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I3" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-02. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>Keten Gömlek (shirt_linen)</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>shirt_linen/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; shirt_linen</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-03. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Boyalı Gömlek (shirt_dyed)</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>shirt_dyed/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; shirt_dyed</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-04. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Yün Kaftan (jacket_wool)</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>jacket_wool/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; jacket_wool</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-05. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Deri Yelek (jacket_leather)</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>jacket_leather/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; jacket_leather</t>
+        </is>
+      </c>
+      <c r="H7" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I7" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-06. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Deri Eldiven (gloves_leather)</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>gloves_leather/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; gloves_leather</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I8" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-07. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Yün Şalvar (pants_wool)</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>pants_wool/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; pants_wool</t>
+        </is>
+      </c>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-08. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>B-09</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Kanvas Şalvar (pants_canvas)</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>pants_canvas/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; pants_canvas</t>
+        </is>
+      </c>
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-09. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Binici Çizmesi (shoes_boots)</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>shoes_boots/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; shoes_boots</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-10. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Sandalet (shoes_sandals)</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>shoes_sandals/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; shoes_sandals</t>
+        </is>
+      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I12" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-11. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Deri Zırh (armor_tier_1)</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>armor_tier_1/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; armor_tier_1</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-12. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>B-13</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Zincir Gömlek (armor_tier_2)</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>armor_tier_2/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; armor_tier_2</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-13. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>B-14</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Plaka Zırh (armor_tier_3)</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>armor_tier_3/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; armor_tier_3</t>
+        </is>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-14. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>B-15</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Kervan Kılıcı (weapon_tier_1)</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>weapon_tier_1/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; weapon_tier_1 --only weapon</t>
+        </is>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-15. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>B-16</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Usta İşi Kılıç (weapon_tier_2)</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>weapon_tier_2/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; weapon_tier_2 --only weapon</t>
+        </is>
+      </c>
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-16. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>B-17</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Şahin Kılıcı (weapon_tier_3)</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>weapon_tier_3/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; weapon_tier_3 --only weapon</t>
+        </is>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-17. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Muska (amulet_ward)</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>amulet_ward/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; amulet_ward --only torso</t>
+        </is>
+      </c>
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-18. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>B-19</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Kurt Dişi (amulet_wolf_fang)</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>amulet_wolf_fang/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; amulet_wolf_fang --only torso</t>
+        </is>
+      </c>
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-19. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>1. Kuşam (giysi/zırh/silah)</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>B-20</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Cesaret Tılsımı (amulet_courage)</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>amulet_courage/ (9 parça PNG)</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Bütün figür, tek resim - sonra kesilir</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>docs/wardrobe/paint_pose_reference.png</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/wardrobe_cut.py &lt;dosya&gt; amulet_courage --only torso</t>
+        </is>
+      </c>
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>Prompt: docs/gemini-prompts-wardrobe.md, B-20. Eski 3x3 parça sayfası yolu terk edildi - yedi tur başarısız oldu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>B-a</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>evt_carcass_on_road</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>e6v_carcass.jpg</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>B-b</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>evt_culture_fisher_catch</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>e6w_fishing.jpg</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H23" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>B-c</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>evt_culture_port_gossip</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>e6x_gossip.jpg</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>B-d</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>evt_culture_valley_dispute</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>e6y_ledger.jpg</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H25" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>B-e</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>evt_forage</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>e6z_forage.jpg</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>B-f</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>evt_hunting_trip</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>e6aa_stag.jpg</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>B-g</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>evt_left_behind_return</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>e6ab_shepherd.jpg</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>B-h</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>evt_military_convoy</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>e6ac_convoy.jpg</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H29" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>B-i</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>evt_mutiny</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>e6ad_unrest.jpg</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>B-j</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>evt_party_investigation</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>e6ae_accusation.jpg</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H31" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>B-k</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>evt_party_theft</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>e6af_theft.jpg</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>B-l</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>evt_profiteer_recognized</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>e6ag_profiteer.jpg</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>B-m</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>evt_refugee_column</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>e6ah_refugees.jpg</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>B-n</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>evt_sick_merchant</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>e6ai_sick.jpg</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H35" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I35" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>B-o</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>evt_spoiled_provisions</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>e6aj_spoiled.jpg</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F36" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I36" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>B-p</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>evt_stress_brawl</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>e6ak_brawl.jpg</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>B-q</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>evt_traveling_tinker</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>e6al_tinker.jpg</t>
+        </is>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F38" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I38" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>2. Olay kartı</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>B-r</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>evt_wanderer_revenge</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>e6am_revenge.jpg</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
+          <t>1:1 tam kadraj illüstrasyon (JPG)</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>Prompt hazır: 'Olay Kartlari 2' sayfası, F sütunu. Geldikten sonra road_journey.gd'nin EVENT_CARD_ART tablosuna satır eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>3. İkon rötuşu</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>p3_agility</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>p3_agility.png</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>Şeffaf PNG ikon</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>Mevcut ikon ailesi</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H40" s="31" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I40" s="31" t="inlineStr">
+        <is>
+          <t>Teslim edilen dosya p3_strength'in neredeyse kopyası (yumruk+halka). İstenen: sıçrayan tavşan. Şu an eski doğru ikon kullanılıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>3. İkon rötuşu</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>p5_scout</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>p5_scout.png</t>
+        </is>
+      </c>
+      <c r="E41" s="32" t="inlineStr">
+        <is>
+          <t>Şeffaf PNG ikon</t>
+        </is>
+      </c>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>Mevcut ikon ailesi</t>
+        </is>
+      </c>
+      <c r="G41" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>Teslim edilen bir insan portresi; ailenin geri kalanı hep nesne. İstenen: eldivenli yumruk üstünde şahin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>3. İkon rötuşu</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>eq_ring_charmed</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>eq_ring_charmed.png</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>Şeffaf PNG ikon</t>
+        </is>
+      </c>
+      <c r="F42" s="32" t="inlineStr">
+        <is>
+          <t>Mevcut ikon ailesi</t>
+        </is>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H42" s="32" t="inlineStr">
+        <is>
+          <t>Düşük</t>
+        </is>
+      </c>
+      <c r="I42" s="32" t="inlineStr">
+        <is>
+          <t>Kullanılabilir durumda; yalnızca mavi boncuk detayı eksik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>3. İkon rötuşu</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>p3_intellect</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>p3_intellect.png</t>
+        </is>
+      </c>
+      <c r="E43" s="32" t="inlineStr">
+        <is>
+          <t>Şeffaf PNG ikon</t>
+        </is>
+      </c>
+      <c r="F43" s="32" t="inlineStr">
+        <is>
+          <t>Mevcut ikon ailesi</t>
+        </is>
+      </c>
+      <c r="G43" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H43" s="32" t="inlineStr">
+        <is>
+          <t>Karar senin</t>
+        </is>
+      </c>
+      <c r="I43" s="32" t="inlineStr">
+        <is>
+          <t>Terazi geldi, defter+kalem istenmişti. Önceki turdan beri oyunda - değiştirmek de bırakmak da savunulabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>3. İkon rötuşu</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>p4_passed_over</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>p4_passed_over.png</t>
+        </is>
+      </c>
+      <c r="E44" s="32" t="inlineStr">
+        <is>
+          <t>Şeffaf PNG ikon</t>
+        </is>
+      </c>
+      <c r="F44" s="32" t="inlineStr">
+        <is>
+          <t>Mevcut ikon ailesi</t>
+        </is>
+      </c>
+      <c r="G44" s="32" t="inlineStr">
+        <is>
+          <t>python3 tools/waybook_ingest_v2.py</t>
+        </is>
+      </c>
+      <c r="H44" s="32" t="inlineStr">
+        <is>
+          <t>Karar senin</t>
+        </is>
+      </c>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>Kırık mühür geldi, kırık asa istenmişti. Aynı durum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>4. Kod (sanat talebi değil)</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Şehir kapısı</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>ArtDraw ile prosedürel çizim</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="31" t="inlineStr">
+        <is>
+          <t>scripts/world/world_hub.gd</t>
+        </is>
+      </c>
+      <c r="H45" s="31" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="inlineStr">
+        <is>
+          <t>Kapı hâlâ düz bir ColorRect (GATE_COLOR, 150x230) - world_hub'daki tek kalan yer tutucu. Boyalı bir doku DEĞİL: dünya sahneleri prosedürel çiziliyor, araya yapıştırılan bir illüstrasyon Art Rules'un 'iki ayrı prodüksiyon' tuzağı olur. Duvar+kemer+kanat ArtDraw ile çizilmeli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>4. Kod (sanat talebi değil)</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>Eşek/köpek oranları</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="32" t="inlineStr">
+        <is>
+          <t>Sabit ayarı</t>
+        </is>
+      </c>
+      <c r="F46" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>world_hub.gd, road_caravan.gd</t>
+        </is>
+      </c>
+      <c r="H46" s="32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>DOG_HEIGHT_RATIO / DONKEY_HEIGHT_RATIO küçük kalmış. Hedef: eşeğin kafası (kulaklarıyla) insan omzu hizasında, köpek diz-bel arasında.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>5. 3B render yolu</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>B-00</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>body (çıplak beden)</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>wardrobe/body_&lt;cinsiyet&gt;_&lt;kilo&gt;/</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>CC0 3B model render'ı</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>Blender Studio Human Base Meshes (CC0)</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="inlineStr">
+        <is>
+          <t>beast_skin.py'nin insan karşılığı (henüz yazılmadı)</t>
+        </is>
+      </c>
+      <c r="H47" s="31" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="inlineStr">
+        <is>
+          <t>Prompt yolu bilerek terk edildi (7 tur). Model dosyası HENÜZ ELDE DEĞİL: main'e yüklenen zip 22 bayt, boş (GitHub web yükleyicisi 25 MB sınırlı). Bugünkü manken yer tutucu olarak çalışıyor.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8408,7 +10672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9437,7 +11701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9603,7 +11867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F45" s="31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/gate/gate_template.png</t>
         </is>
       </c>
       <c r="G45" s="31" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I45" s="31" t="inlineStr">
         <is>
-          <t>Kapı hâlâ düz bir ColorRect (GATE_COLOR, 150x230) - world_hub'daki tek kalan yer tutucu. Boyalı bir doku DEĞİL: dünya sahneleri prosedürel çiziliyor, araya yapıştırılan bir illüstrasyon Art Rules'un 'iki ayrı prodüksiyon' tuzağı olur. Duvar+kemer+kanat ArtDraw ile çizilmeli.</t>
+          <t>Prompt + şablon + palet hazır: docs/gemini-prompts-gate.md. Resim gelince ColorRect -&gt; TextureRect; etkileşim rect aynı kalır.</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="H46" s="32" t="inlineStr">
         <is>
-          <t>Orta</t>
+          <t>TAMAM</t>
         </is>
       </c>
       <c r="I46" s="32" t="inlineStr">
         <is>
-          <t>DOG_HEIGHT_RATIO / DONKEY_HEIGHT_RATIO küçük kalmış. Hedef: eşeğin kafası (kulaklarıyla) insan omzu hizasında, köpek diz-bel arasında.</t>
+          <t>Düzeltildi: eşeğin kafası omuz hizasında (ölçülen %81), köpek diz-bel arasında (%45). Ölçüm tests/screenshot_hub_motion.gd.</t>
         </is>
       </c>
     </row>

--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -10771,7 +10771,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Bu teslimatta hiç gelmedi (kategori B - kıyafet parça sayfaları).</t>
+          <t>ÜRETİLDİ - 3B render ile. tools/human_body_render.py (CC0 Blender Studio Human Base Meshes) boyama pozunda render eder, wardrobe_cut.py dokuz parçaya keser. Altı varyantın (2 cinsiyet x 3 kilo) hepsi oyunda. AI prompt'u ile yeniden istenmeyecek.</t>
         </is>
       </c>
     </row>
@@ -11721,6 +11721,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -11731,6 +11732,7 @@
         <v>123</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -11817,6 +11819,8 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>

--- a/docs/wayborne_gorsel_denetim.xlsx
+++ b/docs/wayborne_gorsel_denetim.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2476,6 +2476,11 @@
           <t>Teslim edilen dosya p3_strength'in neredeyse kopyası (yumruk+halka). İstenen: sıçrayan tavşan. Şu an eski doğru ikon kullanılıyor.</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ÇÖZÜLDÜ (2026-10-22): tavşan, ailenin parşömen diskine oturtuldu (tools/icon_discs.py).</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="32" t="inlineStr">
@@ -2523,6 +2528,11 @@
           <t>Teslim edilen bir insan portresi; ailenin geri kalanı hep nesne. İstenen: eldivenli yumruk üstünde şahin.</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ÇÖZÜLDÜ (2026-10-22): gözcü portresi kalıyor - kullanıcı bu madalyonu örnek tasarım olarak gösterdi.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="32" t="inlineStr">
@@ -2570,6 +2580,11 @@
           <t>Kullanılabilir durumda; yalnızca mavi boncuk detayı eksik.</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ÇÖZÜLDÜ (2026-10-22): kehribar boncuk maviye çevrildi (tools/icon_discs.py).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="32" t="inlineStr">
@@ -2617,6 +2632,11 @@
           <t>Terazi geldi, defter+kalem istenmişti. Önceki turdan beri oyunda - değiştirmek de bırakmak da savunulabilir.</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ÇÖZÜLDÜ (2026-10-22): terazi kalıyor, ailenin diskine oturtuldu.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="32" t="inlineStr">
@@ -2664,6 +2684,11 @@
           <t>Kırık mühür geldi, kırık asa istenmişti. Aynı durum.</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ÇÖZÜLDÜ (2026-10-22): kırık mühür kalıyor - halefiyet sahnesinin çatlak mührüyle (G9b) aynı dil.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="31" t="inlineStr">
@@ -2803,6 +2828,13 @@
       <c r="I47" s="31" t="inlineStr">
         <is>
           <t>Prompt yolu bilerek terk edildi (7 tur). Model dosyası HENÜZ ELDE DEĞİL: main'e yüklenen zip 22 bayt, boş (GitHub web yükleyicisi 25 MB sınırlı). Bugünkü manken yer tutucu olarak çalışıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ek (2026-10-22): p3_endurance gri kare, p3_perception kare karo, p5_crier çıplak çan geliyordu; üçü de ilk teslimatın/ikincinin temiz kaynağından aynı diske oturtuldu.</t>
         </is>
       </c>
     </row>
